--- a/output/topology_excel/2108.xlsx
+++ b/output/topology_excel/2108.xlsx
@@ -425,43 +425,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间ID1</t>
+          <t>房间1</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>房间类型1</t>
+          <t>类型1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>房间ID2</t>
+          <t>面积1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间类型2</t>
+          <t>房间2</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>类型2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>面积2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>连接类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>连接数量</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接面积</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>length</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>width</t>
         </is>
       </c>
     </row>
@@ -475,168 +490,222 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>104864</v>
+      </c>
+      <c r="D2" t="n">
         <v>17</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3000</v>
+        <v>376443</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>120</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>152097</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>212</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5300</v>
+        <v>268322</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>82</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>153549</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1066</v>
+        <v>268322</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>81</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>630764</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F5" t="n">
-        <v>419</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5447</v>
+        <v>126564</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>80</v>
+      </c>
+      <c r="J5" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="inlineStr">
+        <v>630764</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1053</v>
+        <v>57624</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>91</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>268322</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>423</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5499</v>
+        <v>24178</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>81</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -649,81 +718,108 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>630764</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>972</v>
+        <v>20736</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>79</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="inlineStr">
+        <v>268322</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F9" t="n">
-        <v>423</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5278</v>
+        <v>150002</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>80</v>
+      </c>
+      <c r="J9" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>268322</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1365</v>
+        <v>151434</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>81</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -736,255 +832,336 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Hallway</t>
-        </is>
+        <v>630764</v>
+      </c>
+      <c r="D11" t="n">
+        <v>11</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>343</v>
-      </c>
-      <c r="G11" t="n">
-        <v>9883</v>
+        <v>104864</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>82</v>
+      </c>
+      <c r="J11" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>40420</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1053</v>
+        <v>47730</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>85</v>
+      </c>
+      <c r="J12" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>104864</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>154</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2002</v>
+        <v>47730</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>84</v>
+      </c>
+      <c r="J13" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>33408</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1027</v>
+        <v>376443</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>95</v>
+      </c>
+      <c r="J14" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>58928</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>128</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1664</v>
+        <v>33408</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>94</v>
+      </c>
+      <c r="J15" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>68054</v>
+      </c>
+      <c r="D16" t="n">
+        <v>18</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1040</v>
+        <v>439920</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>91</v>
+      </c>
+      <c r="J16" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>376443</v>
+      </c>
+      <c r="D17" t="n">
+        <v>18</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>265</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5655</v>
+        <v>439920</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>窗</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>249</v>
+      </c>
+      <c r="J17" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>630764</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Hallway</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>门/窗</t>
-        </is>
-      </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1053</v>
+        <v>57624</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>343</v>
+      </c>
+      <c r="J18" t="n">
+        <v>251</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" t="inlineStr">
+        <v>630764</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F19" t="n">
-        <v>423</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5499</v>
+        <v>126564</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>577</v>
+      </c>
+      <c r="J19" t="n">
+        <v>158</v>
       </c>
     </row>
     <row r="20">
@@ -997,23 +1174,32 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>630764</v>
+      </c>
+      <c r="D20" t="n">
+        <v>8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1066</v>
+        <v>20736</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>175</v>
+      </c>
+      <c r="J20" t="n">
+        <v>141</v>
       </c>
     </row>
     <row r="21">
@@ -1026,86 +1212,113 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>630764</v>
+      </c>
+      <c r="D21" t="n">
         <v>11</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>104864</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
         <v>290</v>
       </c>
-      <c r="G21" t="n">
-        <v>7371</v>
+      <c r="J21" t="n">
+        <v>188</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>152097</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1105</v>
+        <v>153549</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>363</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>13</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>152097</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1092</v>
+        <v>268322</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>419</v>
+      </c>
+      <c r="J23" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1113,289 +1326,379 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>153549</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2375</v>
+        <v>268322</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>423</v>
+      </c>
+      <c r="J24" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>268322</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>227</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5912</v>
+        <v>24178</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>170</v>
+      </c>
+      <c r="J25" t="n">
+        <v>167</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>268322</v>
+      </c>
+      <c r="D26" t="n">
+        <v>9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1222</v>
+        <v>150002</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>265</v>
+      </c>
+      <c r="J26" t="n">
+        <v>183</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>268322</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1183</v>
+        <v>151434</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>423</v>
+      </c>
+      <c r="J27" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>126564</v>
+      </c>
+      <c r="D28" t="n">
+        <v>8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>296</v>
-      </c>
-      <c r="G28" t="n">
-        <v>3848</v>
+        <v>20736</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>162</v>
+      </c>
+      <c r="J28" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>126564</v>
+      </c>
+      <c r="D29" t="n">
+        <v>12</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>门/窗</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6225</v>
+        <v>40420</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>188</v>
+      </c>
+      <c r="J29" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>18</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>126564</v>
+      </c>
+      <c r="D30" t="n">
+        <v>14</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>611</v>
-      </c>
-      <c r="G30" t="n">
-        <v>15275</v>
+        <v>68054</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>247</v>
+      </c>
+      <c r="J30" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>126564</v>
+      </c>
+      <c r="D31" t="n">
+        <v>13</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
-      </c>
-      <c r="G31" t="n">
-        <v>6569</v>
+        <v>47730</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>222</v>
+      </c>
+      <c r="J31" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>24178</v>
+      </c>
+      <c r="D32" t="n">
+        <v>9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
-      </c>
-      <c r="G32" t="n">
-        <v>4070</v>
+        <v>150002</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>154</v>
+      </c>
+      <c r="J32" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>20736</v>
+      </c>
+      <c r="D33" t="n">
+        <v>11</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>363</v>
-      </c>
-      <c r="G33" t="n">
-        <v>4719</v>
+        <v>104864</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>128</v>
+      </c>
+      <c r="J33" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1403,202 +1706,265 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>150002</v>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>188</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2444</v>
+        <v>151434</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>358</v>
+      </c>
+      <c r="J34" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>104864</v>
+      </c>
+      <c r="D35" t="n">
+        <v>13</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1235</v>
+        <v>47730</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>215</v>
+      </c>
+      <c r="J35" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>18</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
+        <v>104864</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>8</v>
-      </c>
-      <c r="G36" t="n">
-        <v>3936</v>
+        <v>58928</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>24</v>
+      </c>
+      <c r="J36" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>13</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>104864</v>
+      </c>
+      <c r="D37" t="n">
+        <v>18</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>222</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2886</v>
+        <v>439920</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>264</v>
+      </c>
+      <c r="J37" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>104864</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>154</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2002</v>
+        <v>33408</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>144</v>
+      </c>
+      <c r="J38" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>11</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>104864</v>
+      </c>
+      <c r="D39" t="n">
+        <v>17</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>128</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1664</v>
+        <v>376443</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>212</v>
+      </c>
+      <c r="J39" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>40420</v>
+      </c>
+      <c r="D40" t="n">
+        <v>13</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>358</v>
-      </c>
-      <c r="G40" t="n">
-        <v>4654</v>
+        <v>47730</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>215</v>
+      </c>
+      <c r="J40" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1606,28 +1972,37 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>15</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>40420</v>
+      </c>
+      <c r="D41" t="n">
+        <v>14</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>24</v>
-      </c>
-      <c r="G41" t="n">
-        <v>456</v>
+        <v>68054</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>188</v>
+      </c>
+      <c r="J41" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1635,28 +2010,37 @@
         </is>
       </c>
       <c r="C42" t="n">
+        <v>47730</v>
+      </c>
+      <c r="D42" t="n">
         <v>18</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F42" t="n">
-        <v>13</v>
-      </c>
-      <c r="G42" t="n">
-        <v>3432</v>
+        <v>439920</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>264</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1664,28 +2048,37 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>47730</v>
+      </c>
+      <c r="D43" t="n">
+        <v>15</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>144</v>
-      </c>
-      <c r="G43" t="n">
-        <v>2736</v>
+        <v>58928</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>217</v>
+      </c>
+      <c r="J43" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1693,28 +2086,37 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
+        <v>68054</v>
+      </c>
+      <c r="D44" t="n">
+        <v>15</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>188</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3572</v>
+        <v>58928</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>232</v>
+      </c>
+      <c r="J44" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1722,52 +2124,70 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>68054</v>
+      </c>
+      <c r="D45" t="n">
         <v>18</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F45" t="n">
-        <v>5</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1320</v>
+        <v>439920</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>296</v>
+      </c>
+      <c r="J45" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>15</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
+        <v>58928</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>墙</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>217</v>
-      </c>
-      <c r="G46" t="n">
-        <v>4123</v>
+        <v>33408</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>232</v>
+      </c>
+      <c r="J46" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="47">
@@ -1780,23 +2200,32 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>58928</v>
+      </c>
+      <c r="D47" t="n">
         <v>18</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
       <c r="F47" t="n">
+        <v>439920</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
         <v>254</v>
       </c>
-      <c r="G47" t="n">
-        <v>3302</v>
+      <c r="J47" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="48">
@@ -1809,23 +2238,108 @@
         </is>
       </c>
       <c r="C48" t="n">
+        <v>33408</v>
+      </c>
+      <c r="D48" t="n">
+        <v>17</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>376443</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>262</v>
+      </c>
+      <c r="J48" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>16</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>33408</v>
+      </c>
+      <c r="D49" t="n">
         <v>18</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
+      <c r="F49" t="n">
+        <v>439920</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
         <v>144</v>
       </c>
-      <c r="G48" t="n">
-        <v>1872</v>
+      <c r="J49" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>17</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>376443</v>
+      </c>
+      <c r="D50" t="n">
+        <v>18</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>439920</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>墙</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>611</v>
+      </c>
+      <c r="J50" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/2108.xlsx
+++ b/output/topology_excel/2108.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,26 +482,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>104864</v>
+        <v>152097</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>376443</v>
+        <v>268322</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,23 +512,23 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="J2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>152097</v>
+        <v>153549</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
@@ -543,14 +543,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J3" t="n">
         <v>13</v>
@@ -558,40 +558,40 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>153549</v>
+        <v>630764</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>268322</v>
+        <v>126564</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -607,83 +607,83 @@
         <v>630764</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>126564</v>
+        <v>57624</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="J5" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>630764</v>
+        <v>268322</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>57624</v>
+        <v>24178</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="J6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>268322</v>
+        <v>630764</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -691,18 +691,18 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>24178</v>
+        <v>20736</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J7" t="n">
         <v>13</v>
@@ -710,37 +710,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>630764</v>
+        <v>268322</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>20736</v>
+        <v>150002</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="n">
         <v>13</v>
@@ -759,7 +759,7 @@
         <v>268322</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -767,18 +767,18 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>150002</v>
+        <v>151434</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" t="n">
         <v>13</v>
@@ -786,37 +786,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>268322</v>
+        <v>630764</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>151434</v>
+        <v>104864</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" t="n">
         <v>13</v>
@@ -824,18 +824,18 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>630764</v>
+        <v>40420</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -843,18 +843,18 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>104864</v>
+        <v>47730</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J11" t="n">
         <v>13</v>
@@ -862,7 +862,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40420</v>
+        <v>104864</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
@@ -885,14 +885,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J12" t="n">
         <v>13</v>
@@ -900,7 +900,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -908,105 +908,105 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104864</v>
+        <v>33408</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>47730</v>
+        <v>376443</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>58928</v>
+      </c>
+      <c r="D14" t="n">
         <v>16</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>33408</v>
       </c>
-      <c r="D14" t="n">
-        <v>17</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>376443</v>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J14" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>58928</v>
+        <v>68054</v>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>33408</v>
+        <v>439920</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J15" t="n">
         <v>13</v>
@@ -1014,15 +1014,15 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>68054</v>
+        <v>376443</v>
       </c>
       <c r="D16" t="n">
         <v>18</v>
@@ -1037,42 +1037,42 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>窗</t>
+          <t>门</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>91</v>
+        <v>249</v>
       </c>
       <c r="J16" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>104864</v>
+      </c>
+      <c r="D17" t="n">
         <v>17</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Garage</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="F17" t="n">
         <v>376443</v>
       </c>
-      <c r="D17" t="n">
-        <v>18</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>439920</v>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>窗</t>
@@ -1082,7 +1082,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>249</v>
+        <v>120</v>
       </c>
       <c r="J17" t="n">
         <v>25</v>
@@ -1123,7 +1123,7 @@
         <v>343</v>
       </c>
       <c r="J18" t="n">
-        <v>251</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1158,10 +1158,10 @@
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>577</v>
+        <v>436</v>
       </c>
       <c r="J19" t="n">
-        <v>158</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20">
@@ -1234,10 +1234,10 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="J21" t="n">
-        <v>188</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22">
@@ -1424,10 +1424,10 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>265</v>
+        <v>252</v>
       </c>
       <c r="J26" t="n">
-        <v>183</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -1557,7 +1557,7 @@
         <v>126564</v>
       </c>
       <c r="D30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>68054</v>
+        <v>47730</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1576,34 +1576,34 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>Bath</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>24178</v>
+      </c>
+      <c r="D31" t="n">
+        <v>9</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Bedroom</t>
         </is>
       </c>
-      <c r="C31" t="n">
-        <v>126564</v>
-      </c>
-      <c r="D31" t="n">
-        <v>13</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
       <c r="F31" t="n">
-        <v>47730</v>
+        <v>150002</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>222</v>
+        <v>154</v>
       </c>
       <c r="J31" t="n">
         <v>13</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1630,18 +1630,18 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>24178</v>
+        <v>20736</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>150002</v>
+        <v>104864</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="J32" t="n">
         <v>13</v>
@@ -1660,26 +1660,26 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>20736</v>
+        <v>150002</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>104864</v>
+        <v>151434</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>128</v>
+        <v>358</v>
       </c>
       <c r="J33" t="n">
         <v>13</v>
@@ -1698,26 +1698,26 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>150002</v>
+        <v>104864</v>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>151434</v>
+        <v>47730</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>358</v>
+        <v>215</v>
       </c>
       <c r="J34" t="n">
         <v>13</v>
@@ -1747,15 +1747,15 @@
         <v>104864</v>
       </c>
       <c r="D35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>47730</v>
+        <v>58928</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>215</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
@@ -1785,15 +1785,15 @@
         <v>104864</v>
       </c>
       <c r="D36" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>58928</v>
+        <v>33408</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="J36" t="n">
         <v>19</v>
@@ -1823,7 +1823,7 @@
         <v>104864</v>
       </c>
       <c r="D37" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>439920</v>
+        <v>376443</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1842,15 +1842,15 @@
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>264</v>
+        <v>212</v>
       </c>
       <c r="J37" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>104864</v>
+        <v>40420</v>
       </c>
       <c r="D38" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>33408</v>
+        <v>47730</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1880,15 +1880,15 @@
         <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="J38" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1896,18 +1896,18 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>104864</v>
+        <v>40420</v>
       </c>
       <c r="D39" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>376443</v>
+        <v>68054</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1918,15 +1918,15 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="J39" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1934,18 +1934,18 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>40420</v>
+        <v>47730</v>
       </c>
       <c r="D40" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>47730</v>
+        <v>58928</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1956,15 +1956,15 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J40" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1972,18 +1972,18 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40420</v>
+        <v>68054</v>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>68054</v>
+        <v>58928</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1994,15 +1994,15 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="J41" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>47730</v>
+        <v>68054</v>
       </c>
       <c r="D42" t="n">
         <v>18</v>
@@ -2032,34 +2032,34 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>264</v>
+        <v>296</v>
       </c>
       <c r="J42" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>47730</v>
+        <v>58928</v>
       </c>
       <c r="D43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>58928</v>
+        <v>33408</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2070,34 +2070,34 @@
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>68054</v>
+        <v>58928</v>
       </c>
       <c r="D44" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>58928</v>
+        <v>439920</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="J44" t="n">
         <v>13</v>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>68054</v>
+        <v>33408</v>
       </c>
       <c r="D45" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>439920</v>
+        <v>376443</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2146,34 +2146,34 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>296</v>
+        <v>226</v>
       </c>
       <c r="J45" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>58928</v>
+        <v>33408</v>
       </c>
       <c r="D46" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>33408</v>
+        <v>439920</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>232</v>
+        <v>144</v>
       </c>
       <c r="J46" t="n">
         <v>13</v>
@@ -2192,15 +2192,15 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>58928</v>
+        <v>376443</v>
       </c>
       <c r="D47" t="n">
         <v>18</v>
@@ -2222,123 +2222,9 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>254</v>
+        <v>611</v>
       </c>
       <c r="J47" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>16</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>33408</v>
-      </c>
-      <c r="D48" t="n">
-        <v>17</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>376443</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" t="n">
-        <v>262</v>
-      </c>
-      <c r="J48" t="n">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>16</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>33408</v>
-      </c>
-      <c r="D49" t="n">
-        <v>18</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>439920</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" t="n">
-        <v>144</v>
-      </c>
-      <c r="J49" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>17</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>376443</v>
-      </c>
-      <c r="D50" t="n">
-        <v>18</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>439920</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="n">
-        <v>611</v>
-      </c>
-      <c r="J50" t="n">
         <v>25</v>
       </c>
     </row>

--- a/output/topology_excel/2108.xlsx
+++ b/output/topology_excel/2108.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,7 +594,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
         <v>9</v>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>343</v>
+        <v>257</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F19" t="n">
-        <v>145</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,15 +872,15 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="F20" t="n">
-        <v>141</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="n">
         <v>11</v>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>277</v>
+        <v>226</v>
       </c>
       <c r="F21" t="n">
-        <v>115</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>423</v>
+        <v>81</v>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>4</v>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F25" t="n">
-        <v>167</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -993,7 +993,7 @@
         <v>4</v>
       </c>
       <c r="B26" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>252</v>
+        <v>188</v>
       </c>
       <c r="F26" t="n">
         <v>13</v>
@@ -1015,7 +1015,7 @@
         <v>4</v>
       </c>
       <c r="B27" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>423</v>
+        <v>222</v>
       </c>
       <c r="F27" t="n">
         <v>13</v>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="F28" t="n">
         <v>13</v>
@@ -1056,10 +1056,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>188</v>
+        <v>252</v>
       </c>
       <c r="F29" t="n">
         <v>13</v>
@@ -1078,11 +1078,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" t="n">
         <v>6</v>
       </c>
-      <c r="B30" t="n">
-        <v>13</v>
-      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>222</v>
+        <v>358</v>
       </c>
       <c r="F30" t="n">
         <v>13</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B31" t="n">
         <v>9</v>
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>154</v>
+        <v>423</v>
       </c>
       <c r="F31" t="n">
         <v>13</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="F32" t="n">
-        <v>13</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>358</v>
+        <v>175</v>
       </c>
       <c r="F33" t="n">
-        <v>13</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>215</v>
+        <v>128</v>
       </c>
       <c r="F34" t="n">
         <v>13</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B35" t="n">
         <v>15</v>
@@ -1202,19 +1202,19 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>24</v>
+        <v>423</v>
       </c>
       <c r="F35" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>10</v>
+      </c>
+      <c r="B36" t="n">
         <v>11</v>
       </c>
-      <c r="B36" t="n">
-        <v>16</v>
-      </c>
       <c r="C36" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1224,10 +1224,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="F36" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -1235,7 +1235,7 @@
         <v>11</v>
       </c>
       <c r="B37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38">
@@ -1257,7 +1257,7 @@
         <v>12</v>
       </c>
       <c r="B38" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,10 +1268,10 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F38" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
@@ -1279,7 +1279,7 @@
         <v>12</v>
       </c>
       <c r="B39" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>188</v>
+        <v>232</v>
       </c>
       <c r="F39" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>217</v>
+        <v>24</v>
       </c>
       <c r="F40" t="n">
         <v>19</v>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1342,11 +1342,11 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
+        <v>12</v>
+      </c>
+      <c r="B42" t="n">
         <v>14</v>
       </c>
-      <c r="B42" t="n">
-        <v>18</v>
-      </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="F42" t="n">
         <v>13</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B43" t="n">
         <v>16</v>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="F43" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,18 +1400,18 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="F44" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B45" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>226</v>
+        <v>611</v>
       </c>
       <c r="F45" t="n">
         <v>25</v>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>144</v>
+        <v>296</v>
       </c>
       <c r="F46" t="n">
         <v>13</v>
@@ -1452,24 +1452,200 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
+        <v>14</v>
+      </c>
+      <c r="B47" t="n">
+        <v>20</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>144</v>
+      </c>
+      <c r="F47" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>16</v>
+      </c>
+      <c r="B48" t="n">
+        <v>18</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>215</v>
+      </c>
+      <c r="F48" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>16</v>
+      </c>
+      <c r="B49" t="n">
+        <v>20</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>144</v>
+      </c>
+      <c r="F49" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
         <v>17</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B50" t="n">
         <v>18</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="n">
-        <v>611</v>
-      </c>
-      <c r="F47" t="n">
-        <v>25</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>215</v>
+      </c>
+      <c r="F50" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>17</v>
+      </c>
+      <c r="B51" t="n">
+        <v>19</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>188</v>
+      </c>
+      <c r="F51" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>158</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>131</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="n">
+        <v>11</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>192</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" t="n">
+        <v>11</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>74</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/2108.xlsx
+++ b/output/topology_excel/2108.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>13</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>13</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>47</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>15</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>13</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>13</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>13</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>13</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>13</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>13</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>13</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>25</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>13</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>13</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>25</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>25</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>13</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -853,8 +897,10 @@
         <v>433</v>
       </c>
       <c r="F19" t="n">
-        <v>72</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>25</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +947,8 @@
       <c r="F21" t="n">
         <v>13</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +971,8 @@
       <c r="F22" t="n">
         <v>13</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +995,8 @@
       <c r="F23" t="n">
         <v>13</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -963,8 +1017,10 @@
         <v>81</v>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1043,8 @@
       <c r="F25" t="n">
         <v>13</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1067,8 @@
       <c r="F26" t="n">
         <v>13</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1091,8 @@
       <c r="F27" t="n">
         <v>13</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1115,8 @@
       <c r="F28" t="n">
         <v>13</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1139,8 @@
       <c r="F29" t="n">
         <v>13</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1163,8 @@
       <c r="F30" t="n">
         <v>13</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1119,6 +1187,8 @@
       <c r="F31" t="n">
         <v>13</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1133,13 +1203,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="F32" t="n">
-        <v>167</v>
+        <v>13</v>
+      </c>
+      <c r="G32" t="n">
+        <v>157</v>
+      </c>
+      <c r="H32" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="33">
@@ -1155,13 +1231,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>175</v>
+        <v>128</v>
       </c>
       <c r="F33" t="n">
-        <v>141</v>
+        <v>13</v>
+      </c>
+      <c r="G33" t="n">
+        <v>162</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="34">
@@ -1185,6 +1267,8 @@
       <c r="F34" t="n">
         <v>13</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1207,6 +1291,8 @@
       <c r="F35" t="n">
         <v>13</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1315,8 @@
       <c r="F36" t="n">
         <v>15</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1249,8 +1337,10 @@
         <v>277</v>
       </c>
       <c r="F37" t="n">
-        <v>115</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1363,8 @@
       <c r="F38" t="n">
         <v>19</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1387,8 @@
       <c r="F39" t="n">
         <v>13</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1411,8 @@
       <c r="F40" t="n">
         <v>19</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1435,8 @@
       <c r="F41" t="n">
         <v>13</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1459,8 @@
       <c r="F42" t="n">
         <v>13</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1483,8 @@
       <c r="F43" t="n">
         <v>25</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1507,8 @@
       <c r="F44" t="n">
         <v>25</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1427,6 +1531,8 @@
       <c r="F45" t="n">
         <v>25</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1555,8 @@
       <c r="F46" t="n">
         <v>13</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1579,8 @@
       <c r="F47" t="n">
         <v>13</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1603,8 @@
       <c r="F48" t="n">
         <v>13</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1627,8 @@
       <c r="F49" t="n">
         <v>19</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1651,8 @@
       <c r="F50" t="n">
         <v>13</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1559,6 +1675,8 @@
       <c r="F51" t="n">
         <v>19</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1573,7 +1691,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
         <v>158</v>
@@ -1581,13 +1699,19 @@
       <c r="F52" t="n">
         <v>1</v>
       </c>
+      <c r="G52" t="n">
+        <v>131</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1598,15 +1722,17 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" t="n">
         <v>11</v>
@@ -1620,33 +1746,13 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>192</v>
+        <v>74</v>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" t="n">
-        <v>11</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="n">
-        <v>74</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
